--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6526,7 +6526,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122285080</v>
+        <v>122285081</v>
       </c>
       <c r="B48" t="n">
         <v>99478</v>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623749</v>
+        <v>623614</v>
       </c>
       <c r="R48" t="n">
-        <v>6961110</v>
+        <v>6961520</v>
       </c>
       <c r="S48" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Y-Här-0078</t>
+          <t>Y-Här-0080</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6626,11 +6626,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>albård, strandskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6651,7 +6646,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122285081</v>
+        <v>122285072</v>
       </c>
       <c r="B49" t="n">
         <v>99478</v>
@@ -6686,7 +6681,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6696,17 +6691,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mjällådalen, Viksjö S om Ågrena, Ång</t>
+          <t>Mjällådalen, NNO om Gammsågen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623614</v>
+        <v>623741</v>
       </c>
       <c r="R49" t="n">
-        <v>6961520</v>
+        <v>6960641</v>
       </c>
       <c r="S49" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6730,17 +6725,17 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Y-Här-0080</t>
+          <t>Y-Här-0077</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6751,6 +6746,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>lövrik granskog, strandskog, lågor, objekt med naturvärde</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6771,7 +6771,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122285072</v>
+        <v>122285080</v>
       </c>
       <c r="B50" t="n">
         <v>99478</v>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mjällådalen, NNO om Gammsågen, Ång</t>
+          <t>Mjällådalen, Viksjö S om Ågrena, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623741</v>
+        <v>623749</v>
       </c>
       <c r="R50" t="n">
-        <v>6960641</v>
+        <v>6961110</v>
       </c>
       <c r="S50" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6850,17 +6850,17 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Y-Här-0077</t>
+          <t>Y-Här-0078</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2012-10-10</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2012-10-10</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>lövrik granskog, strandskog, lågor, objekt med naturvärde</t>
+          <t>albård, strandskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6529,7 +6529,7 @@
         <v>122285081</v>
       </c>
       <c r="B48" t="n">
-        <v>99478</v>
+        <v>99488</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>122285072</v>
       </c>
       <c r="B49" t="n">
-        <v>99478</v>
+        <v>99488</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>122285080</v>
       </c>
       <c r="B50" t="n">
-        <v>99478</v>
+        <v>99488</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6526,7 +6526,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122285081</v>
+        <v>122285080</v>
       </c>
       <c r="B48" t="n">
         <v>99488</v>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623614</v>
+        <v>623749</v>
       </c>
       <c r="R48" t="n">
-        <v>6961520</v>
+        <v>6961110</v>
       </c>
       <c r="S48" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Y-Här-0080</t>
+          <t>Y-Här-0078</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6626,6 +6626,11 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>albård, strandskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6771,7 +6776,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122285080</v>
+        <v>122285081</v>
       </c>
       <c r="B50" t="n">
         <v>99488</v>
@@ -6806,7 +6811,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6820,13 +6825,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623749</v>
+        <v>623614</v>
       </c>
       <c r="R50" t="n">
-        <v>6961110</v>
+        <v>6961520</v>
       </c>
       <c r="S50" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6850,7 +6855,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Y-Här-0078</t>
+          <t>Y-Här-0080</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -6871,11 +6876,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>albård, strandskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6529,7 +6529,7 @@
         <v>122285080</v>
       </c>
       <c r="B48" t="n">
-        <v>99488</v>
+        <v>99500</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6651,10 +6651,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122285072</v>
+        <v>122285081</v>
       </c>
       <c r="B49" t="n">
-        <v>99488</v>
+        <v>99500</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6696,17 +6696,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mjällådalen, NNO om Gammsågen, Ång</t>
+          <t>Mjällådalen, Viksjö S om Ågrena, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623741</v>
+        <v>623614</v>
       </c>
       <c r="R49" t="n">
-        <v>6960641</v>
+        <v>6961520</v>
       </c>
       <c r="S49" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6730,17 +6730,17 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Y-Här-0077</t>
+          <t>Y-Här-0080</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2012-10-10</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2012-10-10</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6751,11 +6751,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>lövrik granskog, strandskog, lågor, objekt med naturvärde</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6776,10 +6771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122285081</v>
+        <v>122285072</v>
       </c>
       <c r="B50" t="n">
-        <v>99488</v>
+        <v>99500</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6811,7 +6806,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6821,17 +6816,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mjällådalen, Viksjö S om Ågrena, Ång</t>
+          <t>Mjällådalen, NNO om Gammsågen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623614</v>
+        <v>623741</v>
       </c>
       <c r="R50" t="n">
-        <v>6961520</v>
+        <v>6960641</v>
       </c>
       <c r="S50" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6855,17 +6850,17 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Y-Här-0080</t>
+          <t>Y-Här-0077</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6876,6 +6871,11 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>lövrik granskog, strandskog, lågor, objekt med naturvärde</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6529,7 +6529,7 @@
         <v>122285080</v>
       </c>
       <c r="B48" t="n">
-        <v>99500</v>
+        <v>99505</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>122285081</v>
       </c>
       <c r="B49" t="n">
-        <v>99500</v>
+        <v>99505</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>122285072</v>
       </c>
       <c r="B50" t="n">
-        <v>99500</v>
+        <v>99505</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6526,10 +6526,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122285080</v>
+        <v>122285081</v>
       </c>
       <c r="B48" t="n">
-        <v>99505</v>
+        <v>99514</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6544,11 +6544,6 @@
       <c r="E48" t="n">
         <v>345</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Sötgräs</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Cinna latifolia</t>
@@ -6561,7 +6556,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6575,13 +6570,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623749</v>
+        <v>623614</v>
       </c>
       <c r="R48" t="n">
-        <v>6961110</v>
+        <v>6961520</v>
       </c>
       <c r="S48" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6605,7 +6600,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Y-Här-0078</t>
+          <t>Y-Här-0080</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6626,11 +6621,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>albård, strandskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6651,10 +6641,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122285081</v>
+        <v>122285080</v>
       </c>
       <c r="B49" t="n">
-        <v>99505</v>
+        <v>99514</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6669,11 +6659,6 @@
       <c r="E49" t="n">
         <v>345</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Sötgräs</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Cinna latifolia</t>
@@ -6686,7 +6671,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6700,13 +6685,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623614</v>
+        <v>623749</v>
       </c>
       <c r="R49" t="n">
-        <v>6961520</v>
+        <v>6961110</v>
       </c>
       <c r="S49" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6730,7 +6715,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Y-Här-0080</t>
+          <t>Y-Här-0078</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6751,6 +6736,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>albård, strandskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6774,7 +6764,7 @@
         <v>122285072</v>
       </c>
       <c r="B50" t="n">
-        <v>99505</v>
+        <v>99514</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6788,11 +6778,6 @@
       </c>
       <c r="E50" t="n">
         <v>345</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Sötgräs</t>
-        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6526,10 +6526,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122285081</v>
+        <v>122285072</v>
       </c>
       <c r="B48" t="n">
-        <v>99514</v>
+        <v>99527</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6544,6 +6544,11 @@
       <c r="E48" t="n">
         <v>345</v>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Sötgräs</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Cinna latifolia</t>
@@ -6556,7 +6561,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6566,17 +6571,17 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mjällådalen, Viksjö S om Ågrena, Ång</t>
+          <t>Mjällådalen, NNO om Gammsågen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623614</v>
+        <v>623741</v>
       </c>
       <c r="R48" t="n">
-        <v>6961520</v>
+        <v>6960641</v>
       </c>
       <c r="S48" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6600,17 +6605,17 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Y-Här-0080</t>
+          <t>Y-Här-0077</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6621,6 +6626,11 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>lövrik granskog, strandskog, lågor, objekt med naturvärde</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6641,10 +6651,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122285080</v>
+        <v>122285081</v>
       </c>
       <c r="B49" t="n">
-        <v>99514</v>
+        <v>99527</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6659,6 +6669,11 @@
       <c r="E49" t="n">
         <v>345</v>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Sötgräs</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Cinna latifolia</t>
@@ -6671,7 +6686,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6685,13 +6700,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623749</v>
+        <v>623614</v>
       </c>
       <c r="R49" t="n">
-        <v>6961110</v>
+        <v>6961520</v>
       </c>
       <c r="S49" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6715,7 +6730,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Y-Här-0078</t>
+          <t>Y-Här-0080</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6736,11 +6751,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>albård, strandskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6761,10 +6771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122285072</v>
+        <v>122285080</v>
       </c>
       <c r="B50" t="n">
-        <v>99514</v>
+        <v>99527</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6779,6 +6789,11 @@
       <c r="E50" t="n">
         <v>345</v>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sötgräs</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Cinna latifolia</t>
@@ -6791,7 +6806,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6801,17 +6816,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mjällådalen, NNO om Gammsågen, Ång</t>
+          <t>Mjällådalen, Viksjö S om Ågrena, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623741</v>
+        <v>623749</v>
       </c>
       <c r="R50" t="n">
-        <v>6960641</v>
+        <v>6961110</v>
       </c>
       <c r="S50" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6835,17 +6850,17 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Y-Här-0077</t>
+          <t>Y-Här-0078</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2012-10-10</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2012-10-10</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6859,7 +6874,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>lövrik granskog, strandskog, lågor, objekt med naturvärde</t>
+          <t>albård, strandskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6526,10 +6526,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122285072</v>
+        <v>122285081</v>
       </c>
       <c r="B48" t="n">
-        <v>99527</v>
+        <v>99540</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6571,17 +6571,17 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mjällådalen, NNO om Gammsågen, Ång</t>
+          <t>Mjällådalen, Viksjö S om Ågrena, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623741</v>
+        <v>623614</v>
       </c>
       <c r="R48" t="n">
-        <v>6960641</v>
+        <v>6961520</v>
       </c>
       <c r="S48" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6605,17 +6605,17 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Y-Här-0077</t>
+          <t>Y-Här-0080</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2012-10-10</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2012-10-10</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6626,11 +6626,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>lövrik granskog, strandskog, lågor, objekt med naturvärde</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6651,10 +6646,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122285081</v>
+        <v>122285072</v>
       </c>
       <c r="B49" t="n">
-        <v>99527</v>
+        <v>99540</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6686,7 +6681,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6696,17 +6691,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mjällådalen, Viksjö S om Ågrena, Ång</t>
+          <t>Mjällådalen, NNO om Gammsågen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623614</v>
+        <v>623741</v>
       </c>
       <c r="R49" t="n">
-        <v>6961520</v>
+        <v>6960641</v>
       </c>
       <c r="S49" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6730,17 +6725,17 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Y-Här-0080</t>
+          <t>Y-Här-0077</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6751,6 +6746,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>lövrik granskog, strandskog, lågor, objekt med naturvärde</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6774,7 +6774,7 @@
         <v>122285080</v>
       </c>
       <c r="B50" t="n">
-        <v>99527</v>
+        <v>99540</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6526,7 +6526,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122285081</v>
+        <v>122285080</v>
       </c>
       <c r="B48" t="n">
         <v>99540</v>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623614</v>
+        <v>623749</v>
       </c>
       <c r="R48" t="n">
-        <v>6961520</v>
+        <v>6961110</v>
       </c>
       <c r="S48" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Y-Här-0080</t>
+          <t>Y-Här-0078</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6626,6 +6626,11 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>albård, strandskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6771,7 +6776,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122285080</v>
+        <v>122285081</v>
       </c>
       <c r="B50" t="n">
         <v>99540</v>
@@ -6806,7 +6811,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6820,13 +6825,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623749</v>
+        <v>623614</v>
       </c>
       <c r="R50" t="n">
-        <v>6961110</v>
+        <v>6961520</v>
       </c>
       <c r="S50" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6850,7 +6855,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Y-Här-0078</t>
+          <t>Y-Här-0080</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -6871,11 +6876,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>albård, strandskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6526,10 +6526,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122285080</v>
+        <v>122285081</v>
       </c>
       <c r="B48" t="n">
-        <v>99540</v>
+        <v>99543</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623749</v>
+        <v>623614</v>
       </c>
       <c r="R48" t="n">
-        <v>6961110</v>
+        <v>6961520</v>
       </c>
       <c r="S48" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Y-Här-0078</t>
+          <t>Y-Här-0080</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6626,11 +6626,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>albård, strandskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6654,7 +6649,7 @@
         <v>122285072</v>
       </c>
       <c r="B49" t="n">
-        <v>99540</v>
+        <v>99543</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6776,10 +6771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122285081</v>
+        <v>122285080</v>
       </c>
       <c r="B50" t="n">
-        <v>99540</v>
+        <v>99543</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6811,7 +6806,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6825,13 +6820,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623614</v>
+        <v>623749</v>
       </c>
       <c r="R50" t="n">
-        <v>6961520</v>
+        <v>6961110</v>
       </c>
       <c r="S50" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6855,7 +6850,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Y-Här-0080</t>
+          <t>Y-Här-0078</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -6876,6 +6871,11 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>albård, strandskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6526,7 +6526,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122285081</v>
+        <v>122285072</v>
       </c>
       <c r="B48" t="n">
         <v>99543</v>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6571,17 +6571,17 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mjällådalen, Viksjö S om Ågrena, Ång</t>
+          <t>Mjällådalen, NNO om Gammsågen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623614</v>
+        <v>623741</v>
       </c>
       <c r="R48" t="n">
-        <v>6961520</v>
+        <v>6960641</v>
       </c>
       <c r="S48" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6605,17 +6605,17 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Y-Här-0080</t>
+          <t>Y-Här-0077</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
+          <t>2012-10-10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6626,6 +6626,11 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>lövrik granskog, strandskog, lågor, objekt med naturvärde</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6646,7 +6651,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122285072</v>
+        <v>122285080</v>
       </c>
       <c r="B49" t="n">
         <v>99543</v>
@@ -6681,7 +6686,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6691,17 +6696,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mjällådalen, NNO om Gammsågen, Ång</t>
+          <t>Mjällådalen, Viksjö S om Ågrena, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623741</v>
+        <v>623749</v>
       </c>
       <c r="R49" t="n">
-        <v>6960641</v>
+        <v>6961110</v>
       </c>
       <c r="S49" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6725,17 +6730,17 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Y-Här-0077</t>
+          <t>Y-Här-0078</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2012-10-10</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2012-10-10</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6749,7 +6754,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>lövrik granskog, strandskog, lågor, objekt med naturvärde</t>
+          <t>albård, strandskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6771,7 +6776,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122285080</v>
+        <v>122285081</v>
       </c>
       <c r="B50" t="n">
         <v>99543</v>
@@ -6806,7 +6811,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6820,13 +6825,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623749</v>
+        <v>623614</v>
       </c>
       <c r="R50" t="n">
-        <v>6961110</v>
+        <v>6961520</v>
       </c>
       <c r="S50" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6850,7 +6855,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Y-Här-0078</t>
+          <t>Y-Här-0080</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -6871,11 +6876,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>albård, strandskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6529,7 +6529,7 @@
         <v>122285072</v>
       </c>
       <c r="B48" t="n">
-        <v>99543</v>
+        <v>99544</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>122285080</v>
       </c>
       <c r="B49" t="n">
-        <v>99543</v>
+        <v>99544</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>122285081</v>
       </c>
       <c r="B50" t="n">
-        <v>99543</v>
+        <v>99544</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -6529,7 +6529,7 @@
         <v>122285072</v>
       </c>
       <c r="B48" t="n">
-        <v>99544</v>
+        <v>99547</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6651,10 +6651,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122285080</v>
+        <v>122285081</v>
       </c>
       <c r="B49" t="n">
-        <v>99544</v>
+        <v>99547</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6700,13 +6700,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623749</v>
+        <v>623614</v>
       </c>
       <c r="R49" t="n">
-        <v>6961110</v>
+        <v>6961520</v>
       </c>
       <c r="S49" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Y-Här-0078</t>
+          <t>Y-Här-0080</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6751,11 +6751,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>albård, strandskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6776,10 +6771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122285081</v>
+        <v>122285080</v>
       </c>
       <c r="B50" t="n">
-        <v>99544</v>
+        <v>99547</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6811,7 +6806,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6825,13 +6820,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623614</v>
+        <v>623749</v>
       </c>
       <c r="R50" t="n">
-        <v>6961520</v>
+        <v>6961110</v>
       </c>
       <c r="S50" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6855,7 +6850,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Y-Här-0080</t>
+          <t>Y-Här-0078</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -6876,6 +6871,11 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>albård, strandskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 18563-2022 artfynd.xlsx
+++ b/artfynd/A 18563-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/143843</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144337</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144508</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144509</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144510</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144511</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1483,6 +1518,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144512</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1603,6 +1643,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144513</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1718,6 +1763,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144514</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1838,6 +1888,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144527</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1958,6 +2013,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144528</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2073,6 +2133,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144529</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2188,6 +2253,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144530</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2308,6 +2378,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144534</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2428,6 +2503,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144536</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2548,6 +2628,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122285070</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2668,6 +2753,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122285072</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2788,6 +2878,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122285080</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2903,6 +2998,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122285081</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3014,6 +3114,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/192980</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3135,6 +3240,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/192981</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3246,6 +3356,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/192982</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3357,6 +3472,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/192983</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3473,6 +3593,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/199230</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3589,6 +3714,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/199926</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3695,6 +3825,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/199927</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3806,6 +3941,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/209928</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3917,6 +4057,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/209929</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4033,6 +4178,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/345304</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4149,6 +4299,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/346401</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4270,6 +4425,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/346402</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4386,6 +4546,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/346417</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4497,6 +4662,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/346418</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4618,6 +4788,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/346419</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4729,6 +4904,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/346420</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4840,6 +5020,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/346421</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4956,6 +5141,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/346425</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5067,6 +5257,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/346426</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5178,6 +5373,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/346427</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5294,6 +5494,11 @@
           <t>Steget Före</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/384571</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5405,6 +5610,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/389704</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5511,6 +5721,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/389705</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5622,6 +5837,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/389706</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5728,6 +5948,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/389707</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5834,6 +6059,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/389708</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5945,6 +6175,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/389709</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6051,6 +6286,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/389715</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6162,6 +6402,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/425781</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6268,6 +6513,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/391594</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6384,6 +6634,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1126539</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6505,6 +6760,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1126540</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6626,6 +6886,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1126541</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6742,6 +7007,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1126542</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6863,6 +7133,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1677865</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6979,6 +7254,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1837915</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7090,6 +7370,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1852644</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7201,6 +7486,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1873227</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7312,6 +7602,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1873228</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7428,6 +7723,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1958666</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7544,6 +7844,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2062638</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7655,6 +7960,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2710349</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7761,6 +8071,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2710350</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7872,6 +8187,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2710351</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7983,6 +8303,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2712882</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8089,6 +8414,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2712883</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8195,6 +8525,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2712889</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8301,6 +8636,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2712890</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8412,6 +8752,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2712891</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8523,6 +8868,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2712896</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8629,6 +8979,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4887676</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8735,6 +9090,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4818011</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8851,6 +9211,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4823222</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8962,8 +9327,88 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5285185</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>